--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.70272839184115</v>
+        <v>0.926693363674187</v>
       </c>
       <c r="D2" t="n">
-        <v>6.409677220761001</v>
+        <v>1.041572548373663</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56837604062989</v>
+        <v>2.692361106602357</v>
       </c>
       <c r="F2" t="n">
-        <v>16.60484462478168</v>
+        <v>2.698287251527024</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.80123642656037</v>
+        <v>5.330200919316061</v>
       </c>
       <c r="D3" t="n">
-        <v>7.528581012358796</v>
+        <v>1.223394414508304</v>
       </c>
       <c r="E3" t="n">
-        <v>16.56837604062989</v>
+        <v>2.692361106602357</v>
       </c>
       <c r="F3" t="n">
-        <v>16.60484462478168</v>
+        <v>2.698287251527024</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.17458404998362</v>
+        <v>8.478369908122339</v>
       </c>
       <c r="D4" t="n">
-        <v>52.57213150670286</v>
+        <v>8.542971369839215</v>
       </c>
       <c r="E4" t="n">
-        <v>16.56837604062989</v>
+        <v>2.692361106602357</v>
       </c>
       <c r="F4" t="n">
-        <v>16.60484462478168</v>
+        <v>2.698287251527024</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.01886208481613</v>
+        <v>3.253065088782622</v>
       </c>
       <c r="D5" t="n">
-        <v>19.40426692616789</v>
+        <v>3.153193375502282</v>
       </c>
       <c r="E5" t="n">
-        <v>16.56837604062989</v>
+        <v>2.692361106602357</v>
       </c>
       <c r="F5" t="n">
-        <v>16.60484462478168</v>
+        <v>2.698287251527024</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.04041152773306</v>
+        <v>4.231566873256623</v>
       </c>
       <c r="D6" t="n">
-        <v>26.45733932218267</v>
+        <v>4.299317639854684</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56837604062989</v>
+        <v>2.692361106602357</v>
       </c>
       <c r="F6" t="n">
-        <v>16.60484462478168</v>
+        <v>2.698287251527024</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.422039739754768</v>
+        <v>0.5560814577101498</v>
       </c>
       <c r="D7" t="n">
-        <v>5.443507184275646</v>
+        <v>0.8845699174447924</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56837604062989</v>
+        <v>2.692361106602357</v>
       </c>
       <c r="F7" t="n">
-        <v>16.60484462478168</v>
+        <v>2.698287251527024</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
